--- a/2. Components/2.1. Cloud Component/2.1.1. Autonomous_Database/3. autonomous_db_owner (wip)/4. dml/2. location_area [21,24-28,6]/26. admnistrative_unit.xlsx
+++ b/2. Components/2.1. Cloud Component/2.1.1. Autonomous_Database/3. autonomous_db_owner (wip)/4. dml/2. location_area [21,24-28,6]/26. admnistrative_unit.xlsx
@@ -5,16 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dproc\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github_projects\Tech_Hunt_Engine\2. Components\2.1. Cloud Component\2.1.1. Autonomous_Database\3. autonomous_db_owner (wip)\4. dml\2. location_area [21,24-28,6]\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8719B271-A785-454D-82C6-4843FC8EB7CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CB10446-B5DC-4EE4-9764-7AC2016287BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Foaie1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$1668</definedName>
@@ -29,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5211" uniqueCount="4060">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5009" uniqueCount="4058">
   <si>
     <t>name</t>
   </si>
@@ -12197,12 +12196,6 @@
   </si>
   <si>
     <t>RUN</t>
-  </si>
-  <si>
-    <t>Departament</t>
-  </si>
-  <si>
-    <t>Cod</t>
   </si>
   <si>
     <t>MAYO</t>
@@ -12232,18 +12225,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -12258,7 +12245,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -12267,9 +12254,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -12558,7 +12542,7 @@
     <col min="1" max="1" width="23.33203125" customWidth="1"/>
     <col min="2" max="2" width="7.88671875" customWidth="1"/>
     <col min="3" max="3" width="11.109375" customWidth="1"/>
-    <col min="4" max="4" width="7.44140625" customWidth="1"/>
+    <col min="4" max="4" width="7.88671875" customWidth="1"/>
     <col min="6" max="6" width="23.21875" customWidth="1"/>
     <col min="7" max="7" width="26.6640625" customWidth="1"/>
     <col min="8" max="8" width="12.109375" customWidth="1"/>
@@ -16131,7 +16115,7 @@
         <v>304</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>4059</v>
+        <v>4057</v>
       </c>
       <c r="C138" s="2">
         <v>1450000</v>
@@ -16729,7 +16713,7 @@
         <v>332</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>4058</v>
+        <v>4056</v>
       </c>
       <c r="C161" s="2">
         <v>310000</v>
@@ -55937,825 +55921,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F32DC332-429D-41CF-B58A-1AE40023F8B0}">
-  <dimension ref="A1:B101"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="17.88671875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>4056</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4057</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>3993</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>3994</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>3995</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>3996</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>1020</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>1104</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>2244</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>3997</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>3217</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>3998</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>3999</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>1046</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>3090</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>4001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>1135</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>4002</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>4003</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>4004</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>4005</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>1133</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>4006</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>4007</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>4008</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>4009</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>4010</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>4011</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>4012</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>1141</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>4013</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>4014</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>4015</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>4016</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>1418</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>1258</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>4017</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>4018</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>1397</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>4019</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>4020</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>4021</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>4022</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>4023</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>1264</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>4024</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>4025</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A54" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>4026</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>4027</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A56" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>4028</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A57" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>985</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A58" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>2121</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A59" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>4029</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A60" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>899</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A61" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>4030</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A62" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>4031</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A63" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>4032</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A64" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>4033</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A65" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>4034</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>4035</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>2602</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>4036</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A69" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>4037</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A70" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>4038</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A71" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>4039</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A72" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>4040</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A73" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>1768</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A74" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>1343</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A75" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>4041</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A76" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A77" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>4042</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A78" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>4059</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A79" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>4043</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A80" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>4044</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A81" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A82" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A83" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>4045</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A84" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A85" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>3890</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A86" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A87" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>1772</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A88" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>4046</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A89" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>4047</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A90" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>4048</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A91" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>4049</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A92" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A93" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>4050</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A94" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>4051</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A95" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>4052</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A96" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>4053</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A97" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>1069</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A98" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A99" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>4054</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A100" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>4055</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A101" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>4058</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>